--- a/data/trans_camb/P16A06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,86</t>
+          <t>-0,99; 1,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,8</t>
+          <t>-1,11; 1,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,96</t>
+          <t>0,1; 6,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,98</t>
+          <t>-0,46; 0,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,83</t>
+          <t>-0,6; 0,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,09</t>
+          <t>0,37; 4,27</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 390,58</t>
+          <t>-69,13; 536,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,89; 400,09</t>
+          <t>-81,2; 500,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 1282,5</t>
+          <t>-30,89; 1228,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,76; 505,52</t>
+          <t>-65,97; 472,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,29; 522,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 1557,3</t>
+          <t>19,64; 1695,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,49</t>
+          <t>-0,69; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,41</t>
+          <t>-1,11; 0,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,2</t>
+          <t>-0,89; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,02</t>
+          <t>-1,48; 1,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,17</t>
+          <t>-1,31; 1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,85</t>
+          <t>-1,18; 1,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,87</t>
+          <t>-0,79; 0,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,45</t>
+          <t>-0,88; 0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,17</t>
+          <t>-0,67; 1,25</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 477,25</t>
+          <t>-68,35; 594,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 356,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-95,33; 457,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-91,25; 194,38</t>
+          <t>-86,26; 234,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 227,41</t>
+          <t>-74,49; 184,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 298,35</t>
+          <t>-72,07; 298,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,36; 158,76</t>
+          <t>-63,44; 148,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,83; 96,07</t>
+          <t>-69,88; 94,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 212,17</t>
+          <t>-57,7; 214,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,58</t>
+          <t>-0,57; 2,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,63</t>
+          <t>-1,8; 0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,43</t>
+          <t>-0,28; 3,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,09</t>
+          <t>0,45; 4,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,41</t>
+          <t>-1,71; 1,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,59</t>
+          <t>0,2; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,74</t>
+          <t>0,36; 2,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,78</t>
+          <t>-1,39; 0,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,04</t>
+          <t>0,47; 3,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 384,65</t>
+          <t>-39,92; 334,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,51; 103,21</t>
+          <t>-87,86; 138,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 419,42</t>
+          <t>-24,02; 424,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 264,11</t>
+          <t>11,13; 264,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 94,55</t>
+          <t>-55,06; 106,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 232,54</t>
+          <t>-1,82; 226,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,41; 205,51</t>
+          <t>13,39; 207,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 63,12</t>
+          <t>-56,02; 52,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 224,56</t>
+          <t>17,66; 230,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,48</t>
+          <t>-1,17; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,73</t>
+          <t>-0,81; 2,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,91</t>
+          <t>-1,14; 4,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,13</t>
+          <t>-1,25; 4,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 5,47</t>
+          <t>0,41; 5,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,87</t>
+          <t>1,67; 6,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,56</t>
+          <t>-0,72; 2,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,68</t>
+          <t>0,4; 3,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,47</t>
+          <t>0,19; 4,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 235,76</t>
+          <t>-50,27; 325,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 258,22</t>
+          <t>-35,03; 271,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 357,59</t>
+          <t>-35,78; 373,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 136,71</t>
+          <t>-22,76; 157,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 183,9</t>
+          <t>4,26; 196,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,53; 240,73</t>
+          <t>26,17; 236,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 112,15</t>
+          <t>-19,14; 121,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,25; 164,82</t>
+          <t>6,05; 167,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 196,22</t>
+          <t>6,38; 195,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,98</t>
+          <t>-2,52; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,44</t>
+          <t>-1,17; 3,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,7</t>
+          <t>1,71; 6,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,57</t>
+          <t>-2,74; 4,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,67</t>
+          <t>3,15; 11,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,94; 11,54</t>
+          <t>4,53; 11,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,51</t>
+          <t>-1,8; 2,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,51</t>
+          <t>1,58; 6,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,24</t>
+          <t>3,92; 8,23</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 138,49</t>
+          <t>-69,04; 123,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 236,35</t>
+          <t>-38,45; 232,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33,9; 494,88</t>
+          <t>30,0; 405,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 101,9</t>
+          <t>-33,19; 94,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,55; 230,6</t>
+          <t>33,09; 239,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,8; 267,58</t>
+          <t>52,46; 249,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 77,01</t>
+          <t>-32,67; 70,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,38; 181,85</t>
+          <t>27,04; 185,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68,16; 252,58</t>
+          <t>65,72; 258,22</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,82</t>
+          <t>-4,87; 1,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,74</t>
+          <t>-1,82; 5,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,82</t>
+          <t>0,24; 7,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 7,3</t>
+          <t>-1,74; 6,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,9; 13,6</t>
+          <t>3,04; 13,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 8,29</t>
+          <t>-5,85; 8,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,09</t>
+          <t>-2,2; 3,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,72</t>
+          <t>2,22; 8,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,24</t>
+          <t>-3,02; 6,35</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,76; 65,91</t>
+          <t>-71,34; 48,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 158,11</t>
+          <t>-28,24; 149,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1,25; 203,72</t>
+          <t>-3,05; 209,96</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 107,93</t>
+          <t>-17,98; 100,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34,2; 196,79</t>
+          <t>27,33; 192,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 101,14</t>
+          <t>-52,86; 111,98</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 52,04</t>
+          <t>-26,92; 61,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27,02; 151,49</t>
+          <t>24,47; 145,96</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 95,11</t>
+          <t>-34,59; 98,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 1,35</t>
+          <t>-7,92; 1,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 5,11</t>
+          <t>-4,47; 5,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,66</t>
+          <t>2,94; 12,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,02</t>
+          <t>2,88; 13,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,55</t>
+          <t>0,42; 10,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,43; 21,62</t>
+          <t>11,59; 21,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,13</t>
+          <t>0,02; 7,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,3</t>
+          <t>-0,56; 7,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,79; 16,78</t>
+          <t>9,92; 16,83</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 27,31</t>
+          <t>-72,18; 32,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 88,85</t>
+          <t>-41,67; 97,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26,73; 235,3</t>
+          <t>21,0; 227,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24,08; 179,06</t>
+          <t>21,44; 175,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,17; 133,99</t>
+          <t>2,27; 138,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>88,38; 291,11</t>
+          <t>84,91; 285,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,94; 100,91</t>
+          <t>-0,63; 97,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 94,58</t>
+          <t>-5,03; 93,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>80,08; 231,31</t>
+          <t>83,06; 230,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,78</t>
+          <t>-0,62; 0,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,4</t>
+          <t>-0,13; 1,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,78</t>
+          <t>1,63; 3,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,18</t>
+          <t>1,11; 3,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,4</t>
+          <t>2,26; 4,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,04</t>
+          <t>3,72; 6,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,78</t>
+          <t>0,47; 1,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,83</t>
+          <t>1,39; 2,75</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,13</t>
+          <t>3,13; 5,08</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 44,9</t>
+          <t>-27,0; 47,12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 86,63</t>
+          <t>-5,36; 82,98</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>79,08; 229,36</t>
+          <t>70,91; 227,68</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23,92; 85,08</t>
+          <t>23,87; 87,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>45,74; 117,74</t>
+          <t>48,25; 119,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>89,77; 192,54</t>
+          <t>85,29; 189,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,93; 65,96</t>
+          <t>14,49; 63,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>40,08; 100,38</t>
+          <t>40,5; 99,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>99,65; 185,41</t>
+          <t>97,33; 179,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>1,79</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,8</t>
+          <t>-1,08; 1,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,67</t>
+          <t>-1,27; 1,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,75</t>
+          <t>-0,03; 6,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,99</t>
+          <t>-0,41; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,98</t>
+          <t>-0,62; 0,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,27</t>
+          <t>0,33; 3,77</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>247,97%</t>
+          <t>224,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>321,08%</t>
+          <t>340,91%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 536,73</t>
+          <t>-71,81; 459,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,2; 500,33</t>
+          <t>-100,0; 447,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 1228,23</t>
+          <t>-29,95; 1254,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 472,72</t>
+          <t>-59,27; 574,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,29; 522,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 1695,63</t>
+          <t>5,92; 1460,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,51</t>
+          <t>-0,68; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,4</t>
+          <t>-1,17; 0,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,3</t>
+          <t>-0,64; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,13</t>
+          <t>-1,62; 0,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,05</t>
+          <t>-1,27; 1,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,9</t>
+          <t>-1,09; 1,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,9</t>
+          <t>-0,71; 0,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,48</t>
+          <t>-0,9; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,25</t>
+          <t>-0,55; 1,45</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-4,27%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 594,63</t>
+          <t>-77,02; 520,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 196,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,91; 863,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 234,89</t>
+          <t>-88,94; 172,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 184,44</t>
+          <t>-73,41; 214,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,07; 298,49</t>
+          <t>-68,38; 341,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 148,37</t>
+          <t>-61,29; 167,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,88; 94,95</t>
+          <t>-69,29; 99,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 214,38</t>
+          <t>-48,21; 222,99</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,7</t>
+          <t>-0,47; 2,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,67</t>
+          <t>-1,76; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,57</t>
+          <t>-0,41; 2,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,05</t>
+          <t>0,2; 4,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,47</t>
+          <t>-1,56; 1,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,68</t>
+          <t>-0,06; 3,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,83</t>
+          <t>0,05; 2,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,66</t>
+          <t>-1,36; 0,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,1</t>
+          <t>0,18; 2,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105,75%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 334,86</t>
+          <t>-32,93; 336,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,86; 138,02</t>
+          <t>-85,41; 117,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 424,03</t>
+          <t>-27,01; 394,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,13; 264,23</t>
+          <t>1,23; 295,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,06; 106,83</t>
+          <t>-52,04; 112,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 226,94</t>
+          <t>-2,34; 229,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,39; 207,25</t>
+          <t>1,3; 205,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 52,27</t>
+          <t>-55,77; 59,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,66; 230,06</t>
+          <t>6,01; 197,02</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>3,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,78</t>
+          <t>-1,41; 2,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,78</t>
+          <t>-0,74; 3,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,07</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,33</t>
+          <t>-1,11; 4,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,79</t>
+          <t>0,26; 5,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,98</t>
+          <t>1,11; 5,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,61</t>
+          <t>-0,72; 2,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,74</t>
+          <t>0,47; 3,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,62</t>
+          <t>1,7; 4,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>160,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102,24%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>111,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 325,89</t>
+          <t>-52,52; 274,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 271,51</t>
+          <t>-31,48; 354,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 373,23</t>
+          <t>16,77; 549,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 157,62</t>
+          <t>-24,91; 137,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 196,5</t>
+          <t>-0,85; 193,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,17; 236,77</t>
+          <t>18,98; 205,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 121,38</t>
+          <t>-18,61; 120,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 167,67</t>
+          <t>9,42; 169,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 195,14</t>
+          <t>42,95; 226,06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>5,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,82</t>
+          <t>-2,59; 1,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,6</t>
+          <t>-1,24; 3,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,76</t>
+          <t>1,4; 6,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,44</t>
+          <t>-2,58; 4,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 11,12</t>
+          <t>2,61; 10,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,07</t>
+          <t>4,53; 11,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,43</t>
+          <t>-1,71; 2,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,35</t>
+          <t>1,76; 6,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,23</t>
+          <t>3,76; 7,76</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165,01%</t>
+          <t>151,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>125,94%</t>
+          <t>123,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>133,63%</t>
+          <t>129,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 123,32</t>
+          <t>-69,54; 120,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 232,65</t>
+          <t>-38,75; 239,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30,0; 405,95</t>
+          <t>28,24; 423,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 94,0</t>
+          <t>-31,82; 98,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,09; 239,82</t>
+          <t>29,61; 224,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,46; 249,08</t>
+          <t>53,57; 264,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 70,15</t>
+          <t>-29,86; 82,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,04; 185,43</t>
+          <t>29,03; 195,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>65,72; 258,22</t>
+          <t>64,25; 228,47</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>5,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,46</t>
+          <t>-5,1; 1,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,51</t>
+          <t>-1,63; 5,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,14</t>
+          <t>-0,33; 6,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,93</t>
+          <t>-2,32; 6,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,04; 13,46</t>
+          <t>3,43; 13,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 8,85</t>
+          <t>3,43; 11,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,59</t>
+          <t>-2,44; 3,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,59</t>
+          <t>1,83; 8,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,35</t>
+          <t>2,77; 7,92</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,34; 48,56</t>
+          <t>-76,92; 48,02</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 149,45</t>
+          <t>-26,28; 163,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 209,96</t>
+          <t>-6,01; 186,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 100,45</t>
+          <t>-20,64; 99,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27,33; 192,54</t>
+          <t>29,54; 184,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,86; 111,98</t>
+          <t>27,51; 160,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 61,82</t>
+          <t>-28,6; 55,26</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>24,47; 145,96</t>
+          <t>22,39; 142,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 98,73</t>
+          <t>30,12; 134,9</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>16,84</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 1,4</t>
+          <t>-7,71; 1,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 5,02</t>
+          <t>-4,32; 5,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,94; 12,58</t>
+          <t>2,54; 12,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,88; 13,74</t>
+          <t>3,56; 13,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 10,92</t>
+          <t>-0,52; 10,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,59; 21,2</t>
+          <t>12,33; 21,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,74</t>
+          <t>0,35; 7,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 7,13</t>
+          <t>-0,49; 7,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,83</t>
+          <t>9,84; 16,5</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100,3%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>164,27%</t>
+          <t>162,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>141,73%</t>
+          <t>140,41%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 32,05</t>
+          <t>-70,46; 35,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 97,91</t>
+          <t>-41,41; 111,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21,0; 227,58</t>
+          <t>23,36; 246,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,44; 175,52</t>
+          <t>24,11; 182,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,27; 138,2</t>
+          <t>-6,25; 133,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>84,91; 285,46</t>
+          <t>88,07; 277,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 97,96</t>
+          <t>3,21; 106,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 93,25</t>
+          <t>-4,94; 96,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>83,06; 230,96</t>
+          <t>80,87; 223,26</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,75</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,74</t>
+          <t>-0,73; 0,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,41</t>
+          <t>-0,05; 1,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,78</t>
+          <t>2,35; 4,03</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,25</t>
+          <t>1,04; 3,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,51</t>
+          <t>2,31; 4,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,93</t>
+          <t>5,14; 7,3</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,79</t>
+          <t>0,48; 1,82</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,75</t>
+          <t>1,38; 2,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,08</t>
+          <t>4,07; 5,49</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>144,77%</t>
+          <t>159,7%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>136,4%</t>
+          <t>149,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>140,04%</t>
+          <t>153,61%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 47,12</t>
+          <t>-31,25; 45,28</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 82,98</t>
+          <t>-2,85; 85,92</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>70,91; 227,68</t>
+          <t>97,49; 239,76</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23,87; 87,31</t>
+          <t>21,14; 85,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>48,25; 119,9</t>
+          <t>49,66; 120,93</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>85,29; 189,49</t>
+          <t>108,94; 202,2</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,49; 63,92</t>
+          <t>13,58; 64,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>40,5; 99,83</t>
+          <t>40,86; 100,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>97,33; 179,57</t>
+          <t>117,5; 197,17</t>
         </is>
       </c>
     </row>
